--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486776_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486776_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1202</v>
+        <v>6.778</v>
       </c>
       <c r="E2" t="n">
-        <v>5.017</v>
+        <v>5.6996</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1032</v>
+        <v>1.0784</v>
       </c>
       <c r="G2" t="n">
         <v>1.8326</v>
@@ -610,13 +610,13 @@
         <v>3.2823</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9266</v>
+        <v>-0.2688</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7729</v>
+        <v>-0.0902</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1537</v>
+        <v>-0.1786</v>
       </c>
       <c r="V2" t="n">
         <v>4.8281</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2278</v>
+        <v>2.7781</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0919</v>
+        <v>1.9403</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1358</v>
+        <v>0.8378</v>
       </c>
       <c r="G3" t="n">
         <v>1.3023</v>
@@ -688,13 +688,13 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5739</v>
+        <v>0.1242</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0548</v>
+        <v>-0.0968</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5191</v>
+        <v>0.2211</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0972</v>
+        <v>2.0326</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5561</v>
+        <v>2.8391</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4589</v>
+        <v>-0.8065</v>
       </c>
       <c r="G4" t="n">
         <v>0.3294</v>
@@ -766,13 +766,13 @@
         <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5336</v>
+        <v>0.4689</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2407</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2929</v>
+        <v>-0.0548</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6965</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3333</v>
+        <v>1.3788</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8481</v>
+        <v>0.7447</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4852</v>
+        <v>0.6342</v>
       </c>
       <c r="G5" t="n">
         <v>0.379</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5681</v>
+        <v>0.6136</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4136</v>
+        <v>0.3101</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1545</v>
+        <v>0.3035</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1061</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4604</v>
+        <v>0.1088</v>
       </c>
       <c r="F6" t="n">
         <v>0.6457000000000001</v>
@@ -922,10 +922,10 @@
         <v>2.3169</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3863</v>
+        <v>-0.7378</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2477</v>
+        <v>-0.1039</v>
       </c>
       <c r="U6" t="n">
         <v>-0.6339</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. JENKINS BAFFOUR</t>
+          <t>E. RAMÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9602</v>
+        <v>-1.0569</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.923</v>
+        <v>-0.7594</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9628</v>
+        <v>-0.2975</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2294</v>
+        <v>-0.7975</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1722</v>
+        <v>0.4481</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4015</v>
+        <v>-1.2456</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7108</v>
+        <v>-0.2793</v>
       </c>
       <c r="K7" t="n">
-        <v>0.173</v>
+        <v>-0.2409</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8838</v>
+        <v>-0.0384</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5185</v>
+        <v>-0.5182</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0008</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5178</v>
+        <v>-1.2072</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7031</v>
+        <v>1.9308</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7487</v>
+        <v>-0.2827</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9106</v>
+        <v>0.1997</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8381</v>
+        <v>-0.4824</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2455</v>
+        <v>-0.9421</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3709</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6163999999999999</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. RAMÓN FERNÁNDEZ</t>
+          <t>A. JENKINS BAFFOUR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1644</v>
+        <v>-1.1148</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5937</v>
+        <v>-3.3507</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5707</v>
+        <v>2.236</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7975</v>
+        <v>-1.2294</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4481</v>
+        <v>0.1722</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2456</v>
+        <v>-1.4015</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2793</v>
+        <v>-0.7108</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2409</v>
+        <v>0.173</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0384</v>
+        <v>-0.8838</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5182</v>
+        <v>-0.5185</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6889999999999999</v>
+        <v>-0.0008</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2072</v>
+        <v>-0.5178</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9308</v>
+        <v>2.7031</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3902</v>
+        <v>-0.9032</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6347</v>
+        <v>-0.3383</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9421</v>
+        <v>0.2455</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2277</v>
+        <v>0.6163999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. KONTE SYLLA</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.096</v>
+        <v>-3.0941</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8263</v>
+        <v>-2.118</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2697</v>
+        <v>-0.9761</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7236</v>
+        <v>-1.9536</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5503</v>
+        <v>0.393</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1733</v>
+        <v>-2.3466</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9229000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2741</v>
+        <v>0.4626</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6488</v>
+        <v>0.0814</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8008</v>
+        <v>-2.4977</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2763</v>
+        <v>-0.0697</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5245</v>
+        <v>-2.428</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9654</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9654</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0387</v>
+        <v>0.5793</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0273</v>
+        <v>0.2341</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.066</v>
+        <v>0.3452</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3683</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>S. KONTE SYLLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2375</v>
+        <v>-3.2021</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4352</v>
+        <v>-3.0814</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8023</v>
+        <v>-0.1207</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9536</v>
+        <v>-1.7236</v>
       </c>
       <c r="H10" t="n">
-        <v>0.393</v>
+        <v>-0.5503</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3466</v>
+        <v>-1.1733</v>
       </c>
       <c r="J10" t="n">
-        <v>0.544</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4626</v>
+        <v>-0.2741</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0814</v>
+        <v>-0.6488</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4977</v>
+        <v>-0.8008</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0697</v>
+        <v>-0.2763</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.428</v>
+        <v>-0.5245</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3515</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4359</v>
+        <v>-0.1448</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.2278</v>
       </c>
       <c r="U10" t="n">
-        <v>0.519</v>
+        <v>0.083</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3683</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.426499999999999</v>
+        <v>5.254099999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1953</v>
+        <v>2.023000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3.231100000000001</v>
+        <v>3.231300000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2413</v>
@@ -1312,16 +1312,16 @@
         <v>16.4116</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.379</v>
+        <v>-0.5512999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4172000000000002</v>
+        <v>0.4106000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9616999999999999</v>
+        <v>-0.9619000000000002</v>
       </c>
       <c r="V11" t="n">
-        <v>4.254300000000001</v>
+        <v>4.2543</v>
       </c>
       <c r="W11" t="n">
         <v>7.153</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6887</v>
+        <v>3.3933</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9419</v>
+        <v>3.459</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2532</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>2.0169</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4634</v>
+        <v>0.2413</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4968</v>
+        <v>0.0204</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0333</v>
+        <v>0.2209</v>
       </c>
       <c r="V12" t="n">
         <v>0.9421</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8026</v>
+        <v>1.9613</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2862</v>
+        <v>1.1827</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5165</v>
+        <v>0.7785</v>
       </c>
       <c r="G13" t="n">
         <v>0.7821</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.331</v>
+        <v>-0.1724</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3031</v>
+        <v>0.1997</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6341</v>
+        <v>-0.3721</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.077</v>
+        <v>0.8576</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2274</v>
+        <v>4.3308</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1504</v>
+        <v>-3.4732</v>
       </c>
       <c r="G14" t="n">
         <v>1.0097</v>
@@ -1546,13 +1546,13 @@
         <v>1.5446</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5573</v>
+        <v>0.3379</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0832</v>
+        <v>0.0202</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6405</v>
+        <v>0.3177</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8415</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0356</v>
+        <v>0.8114</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8786</v>
+        <v>1.3974</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9142</v>
+        <v>-0.586</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8786</v>
+        <v>2.7758</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7309</v>
+        <v>-0.1382</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8522</v>
+        <v>2.914</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.8436</v>
+        <v>3.2458</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.0064</v>
+        <v>0.759</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1628</v>
+        <v>2.4868</v>
       </c>
       <c r="M15" t="n">
-        <v>0.965</v>
+        <v>-0.47</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2755</v>
+        <v>-0.8972</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6895</v>
+        <v>0.4272</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5792</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>1.335</v>
+        <v>0.4137</v>
       </c>
       <c r="T15" t="n">
-        <v>0.965</v>
+        <v>0.2754</v>
       </c>
       <c r="U15" t="n">
-        <v>0.37</v>
+        <v>0.1383</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.7989</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.712</v>
+        <v>0.6733</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3974</v>
+        <v>1.7348</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6853</v>
+        <v>-1.0615</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7758</v>
+        <v>2.4803</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1382</v>
+        <v>0.448</v>
       </c>
       <c r="I16" t="n">
-        <v>2.914</v>
+        <v>2.0323</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2458</v>
+        <v>2.0671</v>
       </c>
       <c r="K16" t="n">
-        <v>0.759</v>
+        <v>0.7242</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4868</v>
+        <v>1.3428</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.47</v>
+        <v>0.4132</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8972</v>
+        <v>-0.2763</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4272</v>
+        <v>0.6895</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1239</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3144</v>
+        <v>0.2276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2754</v>
+        <v>0.0619</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0389</v>
+        <v>0.1657</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.7989</v>
+        <v>-1.8415</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7989</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5762</v>
+        <v>0.2798</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1898</v>
+        <v>-1.4991</v>
       </c>
       <c r="F17" t="n">
-        <v>0.766</v>
+        <v>1.7789</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8799</v>
+        <v>-0.8786</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2347</v>
+        <v>-1.7309</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3549</v>
+        <v>0.8522</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4099</v>
+        <v>-1.8436</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6133</v>
+        <v>-2.0064</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2035</v>
+        <v>0.1628</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.47</v>
+        <v>0.965</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6214</v>
+        <v>0.2755</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1514</v>
+        <v>0.6895</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5719</v>
+        <v>0.5792</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3786</v>
+        <v>0.3445</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1933</v>
+        <v>0.2347</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3576</v>
+        <v>-0.0028</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4245</v>
+        <v>-1.0171</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.067</v>
+        <v>1.0143</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4803</v>
+        <v>-0.8799</v>
       </c>
       <c r="H18" t="n">
-        <v>0.448</v>
+        <v>-1.2347</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0323</v>
+        <v>0.3549</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0671</v>
+        <v>-0.4099</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7242</v>
+        <v>-0.6133</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3428</v>
+        <v>0.2035</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4132</v>
+        <v>-0.47</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2763</v>
+        <v>-0.6214</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6895</v>
+        <v>0.1514</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0881</v>
+        <v>0.9929</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2484</v>
+        <v>0.5512</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1603</v>
+        <v>0.4416</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8415</v>
+        <v>0.6565</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4128</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GUTIERREZ ROA</t>
+          <t>A. BARBEITO RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4543</v>
+        <v>-1.0026</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7245</v>
+        <v>-1.8781</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2702</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4765</v>
+        <v>1.1363</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2761</v>
+        <v>1.324</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2004</v>
+        <v>-0.1876</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3383</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.3243</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3383</v>
+        <v>-0.6081</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1382</v>
+        <v>0.4201</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2761</v>
+        <v>-0.0003</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1379</v>
+        <v>0.4205</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3862</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1239</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.364</v>
+        <v>0.4483</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3863</v>
+        <v>0.186</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0223</v>
+        <v>0.2622</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BARBEITO RUIZ</t>
+          <t>S. GUTIERREZ ROA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6439</v>
+        <v>-1.6282</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3952</v>
+        <v>-1.7245</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7513</v>
+        <v>0.0964</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1363</v>
+        <v>-1.4765</v>
       </c>
       <c r="H20" t="n">
-        <v>1.324</v>
+        <v>-0.2761</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1876</v>
+        <v>-1.2004</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7161999999999999</v>
+        <v>-1.3383</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3243</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6081</v>
+        <v>-1.3383</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4201</v>
+        <v>-0.1382</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0003</v>
+        <v>-0.2761</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4205</v>
+        <v>0.1379</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.9308</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.193</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3311</v>
+        <v>-0.3863</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1381</v>
+        <v>-0.1516</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0656</v>
+        <v>-3.7042</v>
       </c>
       <c r="E21" t="n">
         <v>-3.9999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.06569999999999999</v>
+        <v>0.2957</v>
       </c>
       <c r="G21" t="n">
         <v>1.1544</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6786</v>
+        <v>-0.3172</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0555</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6231</v>
+        <v>-0.2617</v>
       </c>
       <c r="V21" t="n">
         <v>0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5123</v>
+        <v>-5.3343</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.3206</v>
+        <v>-5.2171</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1917</v>
+        <v>-0.1172</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8793</v>
@@ -2170,13 +2170,13 @@
         <v>1.7377</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2814</v>
+        <v>-0.1035</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3591</v>
+        <v>-0.2557</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07770000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.426400000000001</v>
+        <v>-3.6954</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.231199999999999</v>
+        <v>-3.231099999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1951</v>
+        <v>-0.4642999999999998</v>
       </c>
       <c r="G23" t="n">
         <v>4.241200000000001</v>
@@ -2239,7 +2239,7 @@
         <v>2.859500000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.792400000000001</v>
+        <v>-5.7924</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.4117</v>
@@ -2248,13 +2248,13 @@
         <v>10.6193</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3791</v>
+        <v>2.11</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9616999999999998</v>
+        <v>0.9618</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4171999999999999</v>
+        <v>1.1479</v>
       </c>
       <c r="V23" t="n">
         <v>-4.2542</v>
@@ -2263,7 +2263,7 @@
         <v>2.8987</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.153</v>
+        <v>-7.152999999999999</v>
       </c>
     </row>
   </sheetData>
